--- a/ksoft_old/docs/records/Payment_Term_Records.xlsx
+++ b/ksoft_old/docs/records/Payment_Term_Records.xlsx
@@ -12201,13 +12201,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A02EF43C-C25A-4192-945E-06D7DD139FEF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11DED464-F749-4ABD-95C2-96314A0CB3AE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70AE7435-6CDE-4F2E-BD7C-D7EE49A6E375}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13AB75A0-167D-4394-853D-B84DB4473AA5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A30A9AF-2AEF-41C0-AB3E-FD48A9D01B41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29BB2376-E144-4840-B019-EEBB00379E44}"/>
 </file>
--- a/ksoft_old/docs/records/Payment_Term_Records.xlsx
+++ b/ksoft_old/docs/records/Payment_Term_Records.xlsx
@@ -12201,13 +12201,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11DED464-F749-4ABD-95C2-96314A0CB3AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCD1080E-51C7-4640-AA84-77952928FC76}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13AB75A0-167D-4394-853D-B84DB4473AA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F93413B6-A89D-4B69-822E-DBA5742D9DD7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29BB2376-E144-4840-B019-EEBB00379E44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93B13BCD-F595-4F8F-9167-5A9C56DF1C2C}"/>
 </file>
--- a/ksoft_old/docs/records/Payment_Term_Records.xlsx
+++ b/ksoft_old/docs/records/Payment_Term_Records.xlsx
@@ -12201,13 +12201,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCD1080E-51C7-4640-AA84-77952928FC76}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A02EF43C-C25A-4192-945E-06D7DD139FEF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F93413B6-A89D-4B69-822E-DBA5742D9DD7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70AE7435-6CDE-4F2E-BD7C-D7EE49A6E375}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93B13BCD-F595-4F8F-9167-5A9C56DF1C2C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A30A9AF-2AEF-41C0-AB3E-FD48A9D01B41}"/>
 </file>